--- a/ru/downloads/data-excel/6.4.1.1.xlsx
+++ b/ru/downloads/data-excel/6.4.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3860D95-D5B0-45E5-BC02-4FBB5E56B6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -112,9 +113,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>6.4.1.2 Ташуудан жоготкон суу</t>
-  </si>
-  <si>
     <t>Кыргыз Республикасы</t>
   </si>
   <si>
@@ -160,16 +158,22 @@
     <t>Items</t>
   </si>
   <si>
-    <t>6.4.1.2 Потери воды при транспортировке</t>
-  </si>
-  <si>
-    <t>6.4.1.2 Percentage of water loss during transportation</t>
+    <t>6.4.1.1 Ташуудан жоготкон суу</t>
+  </si>
+  <si>
+    <t>6.4.1.1 Потери воды при транспортировке</t>
+  </si>
+  <si>
+    <t>6.4.1.1 Percentage of water loss during transportation</t>
+  </si>
+  <si>
+    <t>2 417,3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
@@ -391,7 +395,7 @@
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -448,46 +452,40 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
-    <cellStyle name="Normal 17" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="8"/>
-    <cellStyle name="Обычный 11" xfId="21"/>
-    <cellStyle name="Обычный 2" xfId="6"/>
-    <cellStyle name="Обычный 2 2" xfId="9"/>
-    <cellStyle name="Обычный 2 3" xfId="10"/>
-    <cellStyle name="Обычный 3" xfId="11"/>
-    <cellStyle name="Обычный 3 2" xfId="12"/>
-    <cellStyle name="Обычный 4" xfId="4"/>
-    <cellStyle name="Обычный 5" xfId="5"/>
-    <cellStyle name="Обычный 6" xfId="7"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
-    <cellStyle name="Обычный 8" xfId="13"/>
-    <cellStyle name="Обычный 9" xfId="14"/>
-    <cellStyle name="Пояснение 2" xfId="15"/>
-    <cellStyle name="Процентный 2" xfId="16"/>
-    <cellStyle name="Процентный 3" xfId="17"/>
-    <cellStyle name="Стиль 1" xfId="18"/>
-    <cellStyle name="Финансовый 2" xfId="19"/>
-    <cellStyle name="Финансовый 3" xfId="20"/>
+    <cellStyle name="Обычный 10" xfId="8" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 11" xfId="21" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 4" xfId="4" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 5" xfId="5" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 6" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Обычный 8" xfId="13" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Обычный 9" xfId="14" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Пояснение 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Процентный 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Процентный 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Стиль 1" xfId="18" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Финансовый 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Финансовый 3" xfId="20" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -764,8 +762,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="36.28515625" customWidth="1"/>
@@ -773,9 +771,9 @@
     <col min="8" max="8" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="25.5">
+    <row r="1" spans="1:18" ht="25.5">
       <c r="A1" s="7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>43</v>
@@ -789,20 +787,20 @@
       <c r="G1" s="7"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1">
+    <row r="2" spans="1:18" ht="15.75" thickBot="1">
       <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1">
+    <row r="3" spans="1:18" ht="15.75" thickBot="1">
       <c r="A3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="D3" s="10">
         <v>2010</v>
@@ -846,10 +844,13 @@
       <c r="Q3" s="2">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1">
+      <c r="R3" s="2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>1</v>
@@ -868,9 +869,9 @@
       <c r="L4" s="11"/>
       <c r="M4" s="12"/>
     </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1">
+    <row r="5" spans="1:18" ht="15" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -920,10 +921,13 @@
       <c r="Q5" s="14">
         <v>2385.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1">
+      <c r="R5" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>3</v>
@@ -967,16 +971,19 @@
       <c r="O6" s="15">
         <v>109.5</v>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="20">
         <v>103.2</v>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="20">
         <v>112.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1">
+      <c r="R6" s="20">
+        <v>127.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>4</v>
@@ -1020,16 +1027,19 @@
       <c r="O7" s="15">
         <v>210.1</v>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="20">
         <v>231.7</v>
       </c>
-      <c r="Q7" s="22">
+      <c r="Q7" s="20">
         <v>267.89999999999998</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1">
+      <c r="R7" s="20">
+        <v>237.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>5</v>
@@ -1073,16 +1083,19 @@
       <c r="O8" s="15">
         <v>196</v>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="20">
         <v>211.3</v>
       </c>
-      <c r="Q8" s="22">
+      <c r="Q8" s="20">
         <v>230.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1">
+      <c r="R8" s="20">
+        <v>257.39999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>6</v>
@@ -1126,16 +1139,19 @@
       <c r="O9" s="15">
         <v>209</v>
       </c>
-      <c r="P9" s="22">
+      <c r="P9" s="20">
         <v>226.9</v>
       </c>
-      <c r="Q9" s="22">
+      <c r="Q9" s="20">
         <v>249.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1">
+      <c r="R9" s="20">
+        <v>275.89999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>7</v>
@@ -1179,16 +1195,19 @@
       <c r="O10" s="15">
         <v>300.2</v>
       </c>
-      <c r="P10" s="22">
+      <c r="P10" s="20">
         <v>335.3</v>
       </c>
-      <c r="Q10" s="22">
+      <c r="Q10" s="20">
         <v>287</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1">
+      <c r="R10" s="20">
+        <v>304.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>8</v>
@@ -1232,16 +1251,19 @@
       <c r="O11" s="15">
         <v>302.89999999999998</v>
       </c>
-      <c r="P11" s="22">
+      <c r="P11" s="20">
         <v>321.10000000000002</v>
       </c>
-      <c r="Q11" s="22">
+      <c r="Q11" s="20">
         <v>334.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1">
+      <c r="R11" s="20">
+        <v>347.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>9</v>
@@ -1285,16 +1307,19 @@
       <c r="O12" s="15">
         <v>786</v>
       </c>
-      <c r="P12" s="22">
+      <c r="P12" s="20">
         <v>923</v>
       </c>
-      <c r="Q12" s="22">
+      <c r="Q12" s="20">
         <v>851</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1">
+      <c r="R12" s="20">
+        <v>813.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>10</v>
@@ -1338,16 +1363,19 @@
       <c r="O13" s="15">
         <v>27.7</v>
       </c>
-      <c r="P13" s="22">
+      <c r="P13" s="20">
         <v>35.4</v>
       </c>
-      <c r="Q13" s="22">
+      <c r="Q13" s="20">
         <v>48.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1">
+      <c r="R13" s="20">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>11</v>
@@ -1391,16 +1419,19 @@
       <c r="O14" s="15">
         <v>6.8</v>
       </c>
-      <c r="P14" s="22" t="s">
+      <c r="P14" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14" s="20">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1">
+      <c r="R14" s="20">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>12</v>
@@ -1420,12 +1451,13 @@
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1">
-      <c r="A16" s="20" t="s">
-        <v>28</v>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+    </row>
+    <row r="16" spans="1:18" ht="15" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>2</v>
@@ -1469,16 +1501,19 @@
       <c r="O16" s="14">
         <v>26.9</v>
       </c>
-      <c r="P16" s="24">
+      <c r="P16" s="22">
         <v>27.3</v>
       </c>
-      <c r="Q16" s="24">
+      <c r="Q16" s="22">
         <v>26.890545708088244</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1">
-      <c r="A17" s="21" t="s">
-        <v>29</v>
+      <c r="R16" s="22">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>3</v>
@@ -1522,16 +1557,19 @@
       <c r="O17" s="17">
         <v>15.9</v>
       </c>
-      <c r="P17" s="22">
+      <c r="P17" s="20">
         <v>15.1</v>
       </c>
-      <c r="Q17" s="22">
+      <c r="Q17" s="20">
         <v>15.490056759274875</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1">
-      <c r="A18" s="21" t="s">
-        <v>30</v>
+      <c r="R17" s="20">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>4</v>
@@ -1575,16 +1613,19 @@
       <c r="O18" s="17">
         <v>21.7</v>
       </c>
-      <c r="P18" s="22">
+      <c r="P18" s="20">
         <v>21</v>
       </c>
-      <c r="Q18" s="22">
+      <c r="Q18" s="20">
         <v>22.218388220841799</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1">
-      <c r="A19" s="21" t="s">
-        <v>31</v>
+      <c r="R18" s="20">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>5</v>
@@ -1628,16 +1669,19 @@
       <c r="O19" s="17">
         <v>29.9</v>
       </c>
-      <c r="P19" s="22">
+      <c r="P19" s="20">
         <v>29.6</v>
       </c>
-      <c r="Q19" s="22">
+      <c r="Q19" s="20">
         <v>29.614327895683314</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1">
-      <c r="A20" s="21" t="s">
-        <v>32</v>
+      <c r="R19" s="20">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>6</v>
@@ -1681,16 +1725,19 @@
       <c r="O20" s="17">
         <v>30.2</v>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="20">
         <v>29.9</v>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20" s="20">
         <v>30.104452089276922</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1">
-      <c r="A21" s="21" t="s">
-        <v>36</v>
+      <c r="R20" s="20">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
@@ -1734,16 +1781,19 @@
       <c r="O21" s="17">
         <v>24</v>
       </c>
-      <c r="P21" s="22">
+      <c r="P21" s="20">
         <v>24.3</v>
       </c>
-      <c r="Q21" s="22">
+      <c r="Q21" s="20">
         <v>21.825966598728439</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1">
-      <c r="A22" s="21" t="s">
-        <v>33</v>
+      <c r="R21" s="20">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>8</v>
@@ -1787,16 +1837,19 @@
       <c r="O22" s="17">
         <v>31.6</v>
       </c>
-      <c r="P22" s="22">
+      <c r="P22" s="20">
         <v>31.4</v>
       </c>
-      <c r="Q22" s="22">
+      <c r="Q22" s="20">
         <v>32.351574864874735</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1">
-      <c r="A23" s="21" t="s">
-        <v>34</v>
+      <c r="R22" s="20">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>9</v>
@@ -1840,16 +1893,19 @@
       <c r="O23" s="17">
         <v>30.3</v>
       </c>
-      <c r="P23" s="22">
+      <c r="P23" s="20">
         <v>31.5</v>
       </c>
-      <c r="Q23" s="22">
+      <c r="Q23" s="20">
         <v>30.810022297218843</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1">
-      <c r="A24" s="21" t="s">
-        <v>35</v>
+      <c r="R23" s="20">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>10</v>
@@ -1893,16 +1949,19 @@
       <c r="O24" s="17">
         <v>20.7</v>
       </c>
-      <c r="P24" s="22">
+      <c r="P24" s="20">
         <v>23.8</v>
       </c>
-      <c r="Q24" s="22">
+      <c r="Q24" s="20">
         <v>29.193884213235311</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" thickBot="1">
+      <c r="R24" s="20">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15" customHeight="1" thickBot="1">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
@@ -1946,11 +2005,14 @@
       <c r="O25" s="19">
         <v>12</v>
       </c>
-      <c r="P25" s="25" t="s">
+      <c r="P25" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="Q25" s="25">
+      <c r="Q25" s="23">
         <v>7.4362892319581295</v>
+      </c>
+      <c r="R25" s="23">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
